--- a/security-app/信创工具需求清单.xlsx
+++ b/security-app/信创工具需求清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="19200" windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -311,7 +311,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -363,12 +363,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -694,76 +688,76 @@
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1156,7 +1150,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="三线式标题行镶边行表格样式_5ef0b6" count="9" xr9:uid="{EA30B8BB-68A5-4601-95DA-174FBCEBE350}">
+    <tableStyle name="三线式标题行镶边行表格样式_5ef0b6" count="9" xr9:uid="{F1FC49BF-11A7-4EDB-B276-CA62C9B211FE}">
       <tableStyleElement type="wholeTable" dxfId="15"/>
       <tableStyleElement type="headerRow" dxfId="14"/>
       <tableStyleElement type="totalRow" dxfId="13"/>
@@ -1477,7 +1471,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="27" spans="1:6">
+    <row r="3" spans="1:6">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="1" t="s">
@@ -1498,7 +1492,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" ht="40.5" spans="1:6">
+    <row r="6" ht="27" spans="1:6">
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>

--- a/security-app/信创工具需求清单.xlsx
+++ b/security-app/信创工具需求清单.xlsx
@@ -1150,7 +1150,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="三线式标题行镶边行表格样式_5ef0b6" count="9" xr9:uid="{F1FC49BF-11A7-4EDB-B276-CA62C9B211FE}">
+    <tableStyle name="三线式标题行镶边行表格样式_5ef0b6" count="9" xr9:uid="{9F594729-75E7-46AD-923D-8EC4C94FCF0E}">
       <tableStyleElement type="wholeTable" dxfId="15"/>
       <tableStyleElement type="headerRow" dxfId="14"/>
       <tableStyleElement type="totalRow" dxfId="13"/>
